--- a/KBL-Business flow/target/Data/Kbl datas.xlsx
+++ b/KBL-Business flow/target/Data/Kbl datas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>S.NO-0</t>
   </si>
@@ -40,13 +40,16 @@
     <t>mohanraj@123</t>
   </si>
   <si>
+    <t>Test qutation</t>
+  </si>
+  <si>
     <t>D11430150280</t>
   </si>
   <si>
     <t>D41XB00502041033</t>
   </si>
   <si>
-    <t>D11130080576</t>
+    <t>D11130100576</t>
   </si>
   <si>
     <t>kbl@123</t>
@@ -58,7 +61,7 @@
     <t>Ready To Ship</t>
   </si>
   <si>
-    <t>CND699580044</t>
+    <t>CNG770940074</t>
   </si>
   <si>
     <t>dattatray.jadhav@kbl.co.in</t>
@@ -73,7 +76,7 @@
     <t>KBLSTAGE46885</t>
   </si>
   <si>
-    <t>CAD699580044</t>
+    <t>CAR286790084</t>
   </si>
 </sst>
 </file>
@@ -521,7 +524,9 @@
         <v>620007</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
@@ -566,7 +571,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -578,7 +583,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -590,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -602,7 +607,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -614,7 +619,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -626,7 +631,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -638,7 +643,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -662,7 +667,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -674,7 +679,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -686,7 +691,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -698,7 +703,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -710,7 +715,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
